--- a/artfynd/A 59864-2021 artfynd.xlsx
+++ b/artfynd/A 59864-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59864-2021 artfynd.xlsx
+++ b/artfynd/A 59864-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112164579</v>
+        <v>112164673</v>
       </c>
       <c r="B2" t="n">
-        <v>93361</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2666</v>
+        <v>1078</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Rundfjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neckera crispa</t>
+          <t>Alleniella besseri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Lobarz.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>332923</v>
+        <v>332854</v>
       </c>
       <c r="R2" t="n">
-        <v>6626955</v>
+        <v>6626967</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,6 +750,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Under överhängande klippa</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112164702</v>
+        <v>112164565</v>
       </c>
       <c r="B3" t="n">
-        <v>89556</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,26 +793,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>2362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>332980</v>
+        <v>332934</v>
       </c>
       <c r="R3" t="n">
-        <v>6627033</v>
+        <v>6626957</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,15 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112164565</v>
+        <v>112164609</v>
       </c>
       <c r="B4" t="n">
-        <v>92884</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95944</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>332935</v>
+        <v>332973</v>
       </c>
       <c r="R4" t="n">
-        <v>6626957</v>
+        <v>6627007</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,15 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112164607</v>
+        <v>112189008</v>
       </c>
       <c r="B5" t="n">
-        <v>93357</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2667</v>
+        <v>2609</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsfliksmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lejeunea cavifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ehrh.) Lindb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>332973</v>
+        <v>332854</v>
       </c>
       <c r="R5" t="n">
-        <v>6627007</v>
+        <v>6626967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,15 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112164609</v>
+        <v>112164579</v>
       </c>
       <c r="B6" t="n">
-        <v>92884</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2362</v>
+        <v>2666</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>332973</v>
+        <v>332923</v>
       </c>
       <c r="R6" t="n">
-        <v>6627007</v>
+        <v>6626955</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,37 +1190,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112164673</v>
+        <v>112164561</v>
       </c>
       <c r="B7" t="n">
-        <v>93356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1078</v>
+        <v>2667</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rundfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alleniella besseri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lobarz.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>332854</v>
+        <v>332934</v>
       </c>
       <c r="R7" t="n">
-        <v>6626968</v>
+        <v>6626957</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,11 +1265,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-06-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Under överhängande klippa</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,42 +1292,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112164661</v>
+        <v>112164607</v>
       </c>
       <c r="B8" t="n">
-        <v>90051</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5467</v>
+        <v>2667</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1364,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>332865</v>
+        <v>332973</v>
       </c>
       <c r="R8" t="n">
-        <v>6626972</v>
+        <v>6627007</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,11 +1367,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-06-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,15 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112164561</v>
+        <v>112164702</v>
       </c>
       <c r="B9" t="n">
-        <v>93357</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1448,27 +1405,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2667</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1476,10 +1432,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>332935</v>
+        <v>332980</v>
       </c>
       <c r="R9" t="n">
-        <v>6626957</v>
+        <v>6627033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,43 +1495,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112189008</v>
+        <v>112164661</v>
       </c>
       <c r="B10" t="n">
-        <v>95441</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2609</v>
+        <v>5467</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsfliksmossa</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lejeunea cavifolia</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ehrh.) Lindb.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1583,10 +1533,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>332854</v>
+        <v>332864</v>
       </c>
       <c r="R10" t="n">
-        <v>6626968</v>
+        <v>6626972</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,6 +1571,11 @@
           <t>2022-06-07</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1643,6 +1598,103 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>108953438</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Påterud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>332943</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6626936</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59864-2021 artfynd.xlsx
+++ b/artfynd/A 59864-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112164673</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112164565</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112164609</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112189008</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112164579</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112164561</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112164607</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112164702</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1598,6 +1643,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112164661</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1695,8 +1745,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108953438</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>